--- a/research/traditional_assets/database/data/belgium/belgium_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0212</v>
+        <v>0.0128</v>
       </c>
       <c r="E2">
-        <v>0.2064</v>
+        <v>0.185</v>
       </c>
       <c r="G2">
-        <v>0.7671401250708706</v>
+        <v>1.182809471060648</v>
       </c>
       <c r="H2">
-        <v>0.7671401250708706</v>
+        <v>1.182809471060648</v>
       </c>
       <c r="I2">
-        <v>0.8185985800478959</v>
+        <v>0.7228876273116097</v>
       </c>
       <c r="J2">
-        <v>0.782624828533757</v>
+        <v>0.6934359432818874</v>
       </c>
       <c r="K2">
-        <v>325.038</v>
+        <v>-10.862</v>
       </c>
       <c r="L2">
-        <v>0.6876316925185957</v>
+        <v>-0.0417782085602634</v>
       </c>
       <c r="M2">
-        <v>64.571</v>
+        <v>61.571</v>
       </c>
       <c r="N2">
-        <v>0.02969832998348841</v>
+        <v>0.03532614620208499</v>
       </c>
       <c r="O2">
-        <v>0.1986567724389148</v>
+        <v>-5.668477260173082</v>
       </c>
       <c r="P2">
-        <v>62.21100000000001</v>
+        <v>59.911</v>
       </c>
       <c r="Q2">
-        <v>0.02861288824089448</v>
+        <v>0.03437372699993689</v>
       </c>
       <c r="R2">
-        <v>0.1913960829195356</v>
+        <v>-5.515650893021544</v>
       </c>
       <c r="S2">
-        <v>2.359999999999999</v>
+        <v>1.659999999999997</v>
       </c>
       <c r="T2">
-        <v>0.0365489151476669</v>
+        <v>0.02696074450634222</v>
       </c>
       <c r="U2">
-        <v>489.99</v>
+        <v>196.09</v>
       </c>
       <c r="V2">
-        <v>0.2253625421413558</v>
+        <v>0.1125059526200134</v>
       </c>
       <c r="W2">
-        <v>0.07336523125996809</v>
+        <v>0.006620209059233449</v>
       </c>
       <c r="X2">
-        <v>0.0502257353614094</v>
+        <v>0.0807334440526585</v>
       </c>
       <c r="Y2">
-        <v>0.0231394958985587</v>
+        <v>-0.07411323499342505</v>
       </c>
       <c r="Z2">
-        <v>0.2694101715317484</v>
+        <v>0.1262192670901291</v>
       </c>
       <c r="AA2">
-        <v>0.09151990543166837</v>
+        <v>0.06942230394439659</v>
       </c>
       <c r="AB2">
-        <v>0.04817272237335087</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC2">
-        <v>0.04334718305831749</v>
+        <v>-0.008919039736713805</v>
       </c>
       <c r="AD2">
-        <v>408.517</v>
+        <v>346.417</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>408.517</v>
+        <v>346.417</v>
       </c>
       <c r="AG2">
-        <v>-81.47300000000001</v>
+        <v>150.327</v>
       </c>
       <c r="AH2">
-        <v>0.1581715127343096</v>
+        <v>0.1658015638378881</v>
       </c>
       <c r="AI2">
-        <v>0.1594961458979572</v>
+        <v>0.163605124594018</v>
       </c>
       <c r="AJ2">
-        <v>-0.038930941337193</v>
+        <v>0.07940126459323801</v>
       </c>
       <c r="AK2">
-        <v>-0.03933410160830818</v>
+        <v>0.07824205085392394</v>
       </c>
       <c r="AL2">
-        <v>11.744</v>
+        <v>10.521</v>
       </c>
       <c r="AM2">
-        <v>11.105</v>
+        <v>10.034</v>
       </c>
       <c r="AN2">
-        <v>1.052065413340201</v>
+        <v>1.828058047493404</v>
       </c>
       <c r="AO2">
-        <v>32.94831403269755</v>
+        <v>17.86379621708963</v>
       </c>
       <c r="AP2">
-        <v>-0.2098197270151945</v>
+        <v>0.7932823218997362</v>
       </c>
       <c r="AQ2">
-        <v>34.84421431787483</v>
+        <v>18.73081522822403</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GIMV NV (ENXTBR:GIMB)</t>
+          <t>Gimv NV (ENXTBR:GIMB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0212</v>
-      </c>
-      <c r="E3">
-        <v>0.0958</v>
+        <v>0.0128</v>
       </c>
       <c r="G3">
-        <v>0.7544107268877911</v>
+        <v>1.24243813015582</v>
       </c>
       <c r="H3">
-        <v>0.7544107268877911</v>
+        <v>1.24243813015582</v>
       </c>
       <c r="I3">
-        <v>0.8115737473535638</v>
+        <v>0.694775435380385</v>
       </c>
       <c r="J3">
-        <v>0.8095309388003098</v>
+        <v>0.694775435380385</v>
       </c>
       <c r="K3">
-        <v>288.2</v>
+        <v>-37</v>
       </c>
       <c r="L3">
-        <v>0.6779581274994119</v>
+        <v>-0.1695692025664528</v>
       </c>
       <c r="M3">
-        <v>44.56</v>
+        <v>44.26</v>
       </c>
       <c r="N3">
-        <v>0.02759816672860151</v>
+        <v>0.03531758697733801</v>
       </c>
       <c r="O3">
-        <v>0.1546148507980569</v>
+        <v>-1.196216216216216</v>
       </c>
       <c r="P3">
-        <v>42.2</v>
+        <v>42.6</v>
       </c>
       <c r="Q3">
-        <v>0.02613650439737396</v>
+        <v>0.03399297797638046</v>
       </c>
       <c r="R3">
-        <v>0.1464260929909785</v>
+        <v>-1.151351351351351</v>
       </c>
       <c r="S3">
-        <v>2.359999999999999</v>
+        <v>1.659999999999997</v>
       </c>
       <c r="T3">
-        <v>0.05296229802513464</v>
+        <v>0.0375056484410302</v>
       </c>
       <c r="U3">
-        <v>456.6</v>
+        <v>157.2</v>
       </c>
       <c r="V3">
-        <v>0.2827945001858045</v>
+        <v>0.1254388764762209</v>
       </c>
       <c r="W3">
-        <v>0.2109192037470726</v>
+        <v>-0.02321204516938519</v>
       </c>
       <c r="X3">
-        <v>0.05444375789583407</v>
+        <v>0.08653153222725167</v>
       </c>
       <c r="Y3">
-        <v>0.1564754458512385</v>
+        <v>-0.1097435773966369</v>
       </c>
       <c r="Z3">
-        <v>0.3250745583849507</v>
+        <v>0.1411749482401656</v>
       </c>
       <c r="AA3">
-        <v>0.2631579124294652</v>
+        <v>0.09808488612836438</v>
       </c>
       <c r="AB3">
-        <v>0.04776885343900261</v>
+        <v>0.07667290813744146</v>
       </c>
       <c r="AC3">
-        <v>0.2153890589904626</v>
+        <v>0.02141197799092293</v>
       </c>
       <c r="AD3">
-        <v>408.2</v>
+        <v>346.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>408.2</v>
+        <v>346.1</v>
       </c>
       <c r="AG3">
-        <v>-48.40000000000003</v>
+        <v>188.9</v>
       </c>
       <c r="AH3">
-        <v>0.2017994858611825</v>
+        <v>0.2164071781404364</v>
       </c>
       <c r="AI3">
-        <v>0.2028423772609819</v>
+        <v>0.212762033564886</v>
       </c>
       <c r="AJ3">
-        <v>-0.03090282211722643</v>
+        <v>0.1309895291588656</v>
       </c>
       <c r="AK3">
-        <v>-0.03110939709474228</v>
+        <v>0.1285471248724056</v>
       </c>
       <c r="AL3">
-        <v>11.6</v>
+        <v>10.3</v>
       </c>
       <c r="AM3">
-        <v>11.211</v>
+        <v>10.03</v>
       </c>
       <c r="AN3">
-        <v>1.179087232813403</v>
+        <v>2.263570961412688</v>
       </c>
       <c r="AO3">
-        <v>29.74137931034483</v>
+        <v>14.71844660194175</v>
       </c>
       <c r="AP3">
-        <v>-0.1398035817446564</v>
+        <v>1.235448005232178</v>
       </c>
       <c r="AQ3">
-        <v>30.77334760503077</v>
+        <v>15.11465603190429</v>
       </c>
     </row>
     <row r="4">
@@ -856,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.255</v>
+        <v>0.236</v>
       </c>
       <c r="E4">
-        <v>0.317</v>
+        <v>0.185</v>
       </c>
       <c r="G4">
-        <v>0.8881856540084389</v>
+        <v>0.8798076923076923</v>
       </c>
       <c r="H4">
-        <v>0.8881856540084389</v>
+        <v>0.8798076923076923</v>
       </c>
       <c r="I4">
-        <v>0.8881856540084389</v>
+        <v>0.8774038461538461</v>
       </c>
       <c r="J4">
-        <v>0.8599781831068586</v>
+        <v>0.8557634005453502</v>
       </c>
       <c r="K4">
-        <v>36.8</v>
+        <v>26.1</v>
       </c>
       <c r="L4">
-        <v>0.7763713080168776</v>
+        <v>0.6274038461538461</v>
       </c>
       <c r="M4">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="N4">
-        <v>0.03562432529686938</v>
+        <v>0.03519967064635653</v>
       </c>
       <c r="O4">
-        <v>0.5380434782608696</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="P4">
-        <v>19.8</v>
+        <v>17.1</v>
       </c>
       <c r="Q4">
-        <v>0.03562432529686938</v>
+        <v>0.03519967064635653</v>
       </c>
       <c r="R4">
-        <v>0.5380434782608696</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,31 +901,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>30.1</v>
+        <v>35.6</v>
       </c>
       <c r="V4">
-        <v>0.05415617128463477</v>
+        <v>0.07328118567311651</v>
       </c>
       <c r="W4">
-        <v>0.07336523125996809</v>
+        <v>0.04807515196168724</v>
       </c>
       <c r="X4">
-        <v>0.04817272237335087</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="Y4">
-        <v>0.02519250888661722</v>
+        <v>-0.03026619171942316</v>
       </c>
       <c r="Z4">
-        <v>0.1064211944319712</v>
+        <v>0.08112324492979721</v>
       </c>
       <c r="AA4">
-        <v>0.09151990543166837</v>
+        <v>0.06942230394439659</v>
       </c>
       <c r="AB4">
-        <v>0.04817272237335087</v>
+        <v>0.0783413436811104</v>
       </c>
       <c r="AC4">
-        <v>0.04334718305831749</v>
+        <v>-0.008919039736713805</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -940,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-30.1</v>
+        <v>-35.6</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -949,28 +946,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.05725699067909455</v>
+        <v>-0.0790759662372279</v>
       </c>
       <c r="AK4">
-        <v>-0.05869734789391576</v>
+        <v>-0.079269650411935</v>
       </c>
       <c r="AL4">
-        <v>0.107</v>
+        <v>0.184</v>
       </c>
       <c r="AM4">
-        <v>-0.131</v>
+        <v>-0.02099999999999999</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>393.4579439252337</v>
+        <v>198.3695652173913</v>
       </c>
       <c r="AP4">
-        <v>-0.7149643705463183</v>
+        <v>-0.9726775956284153</v>
       </c>
       <c r="AQ4">
-        <v>-321.3740458015267</v>
+        <v>-1738.095238095239</v>
       </c>
     </row>
     <row r="5">
@@ -1014,7 +1011,7 @@
         <v>0.211</v>
       </c>
       <c r="N5">
-        <v>0.05509138381201044</v>
+        <v>0.05368956743002544</v>
       </c>
       <c r="O5">
         <v>5.552631578947368</v>
@@ -1023,7 +1020,7 @@
         <v>0.211</v>
       </c>
       <c r="Q5">
-        <v>0.05509138381201044</v>
+        <v>0.05368956743002544</v>
       </c>
       <c r="R5">
         <v>5.552631578947368</v>
@@ -1038,16 +1035,16 @@
         <v>3.29</v>
       </c>
       <c r="V5">
-        <v>0.8590078328981723</v>
+        <v>0.8371501272264631</v>
       </c>
       <c r="W5">
         <v>0.006620209059233449</v>
       </c>
       <c r="X5">
-        <v>0.0502257353614094</v>
+        <v>0.0807334440526585</v>
       </c>
       <c r="Y5">
-        <v>-0.04360552630217595</v>
+        <v>-0.07411323499342505</v>
       </c>
       <c r="Z5">
         <v>0.1329639889196675</v>
@@ -1056,10 +1053,10 @@
         <v>-0.09686845483413278</v>
       </c>
       <c r="AB5">
-        <v>0.04828448108305795</v>
+        <v>0.07840966213082375</v>
       </c>
       <c r="AC5">
-        <v>-0.1451529359171907</v>
+        <v>-0.1752781169649565</v>
       </c>
       <c r="AD5">
         <v>0.317</v>
@@ -1074,13 +1071,13 @@
         <v>-2.973</v>
       </c>
       <c r="AH5">
-        <v>0.07644080057873161</v>
+        <v>0.07464092300447375</v>
       </c>
       <c r="AI5">
         <v>0.05285976321494081</v>
       </c>
       <c r="AJ5">
-        <v>-3.469078179696615</v>
+        <v>-3.106583072100312</v>
       </c>
       <c r="AK5">
         <v>-1.098263760620613</v>

--- a/research/traditional_assets/database/data/belgium/belgium_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0128</v>
+        <v>0.234</v>
       </c>
       <c r="E2">
-        <v>0.185</v>
+        <v>0.1025</v>
       </c>
       <c r="G2">
-        <v>1.182809471060648</v>
+        <v>0.0007150153217568924</v>
       </c>
       <c r="H2">
-        <v>1.182809471060648</v>
+        <v>0.0007150153217568924</v>
       </c>
       <c r="I2">
-        <v>0.7228876273116097</v>
+        <v>0.4471569628873</v>
       </c>
       <c r="J2">
-        <v>0.6934359432818874</v>
+        <v>0.3630559547714823</v>
       </c>
       <c r="K2">
-        <v>-10.862</v>
+        <v>213.169</v>
       </c>
       <c r="L2">
-        <v>-0.0417782085602634</v>
+        <v>0.3629026217228465</v>
       </c>
       <c r="M2">
-        <v>61.571</v>
+        <v>66.67599999999999</v>
       </c>
       <c r="N2">
-        <v>0.03532614620208499</v>
+        <v>0.03578958668813741</v>
       </c>
       <c r="O2">
-        <v>-5.668477260173082</v>
+        <v>0.3127846919580238</v>
       </c>
       <c r="P2">
-        <v>59.911</v>
+        <v>65.8</v>
       </c>
       <c r="Q2">
-        <v>0.03437372699993689</v>
+        <v>0.03531937734836285</v>
       </c>
       <c r="R2">
-        <v>-5.515650893021544</v>
+        <v>0.3086752764238702</v>
       </c>
       <c r="S2">
-        <v>1.659999999999997</v>
+        <v>0.8759999999999977</v>
       </c>
       <c r="T2">
-        <v>0.02696074450634222</v>
+        <v>0.01313816065750792</v>
       </c>
       <c r="U2">
-        <v>196.09</v>
+        <v>233.31</v>
       </c>
       <c r="V2">
-        <v>0.1125059526200134</v>
+        <v>0.1252334943639291</v>
       </c>
       <c r="W2">
-        <v>0.006620209059233449</v>
+        <v>0.05811044833557821</v>
       </c>
       <c r="X2">
-        <v>0.0807334440526585</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y2">
-        <v>-0.07411323499342505</v>
+        <v>-0.008678079014833598</v>
       </c>
       <c r="Z2">
-        <v>0.1262192670901291</v>
+        <v>0.3025386671611119</v>
       </c>
       <c r="AA2">
-        <v>0.06942230394439659</v>
+        <v>0.1177591814900668</v>
       </c>
       <c r="AB2">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC2">
-        <v>-0.008919039736713805</v>
+        <v>0.05097065413965503</v>
       </c>
       <c r="AD2">
-        <v>346.417</v>
+        <v>373.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>346.417</v>
+        <v>373.2</v>
       </c>
       <c r="AG2">
-        <v>150.327</v>
+        <v>139.89</v>
       </c>
       <c r="AH2">
-        <v>0.1658015638378881</v>
+        <v>0.1668902602629461</v>
       </c>
       <c r="AI2">
-        <v>0.163605124594018</v>
+        <v>0.1553834624031976</v>
       </c>
       <c r="AJ2">
-        <v>0.07940126459323801</v>
+        <v>0.06984407531117535</v>
       </c>
       <c r="AK2">
-        <v>0.07824205085392394</v>
+        <v>0.06451032746288891</v>
       </c>
       <c r="AL2">
-        <v>10.521</v>
+        <v>12.489</v>
       </c>
       <c r="AM2">
-        <v>10.034</v>
+        <v>7.435000000000001</v>
       </c>
       <c r="AN2">
-        <v>1.828058047493404</v>
+        <v>1.406391317455532</v>
       </c>
       <c r="AO2">
-        <v>17.86379621708963</v>
+        <v>21.03130755064457</v>
       </c>
       <c r="AP2">
-        <v>0.7932823218997362</v>
+        <v>0.5271706361169731</v>
       </c>
       <c r="AQ2">
-        <v>18.73081522822403</v>
+        <v>35.32750504371217</v>
       </c>
     </row>
     <row r="3">
@@ -722,118 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0128</v>
+        <v>0.0302</v>
+      </c>
+      <c r="E3">
+        <v>0.102</v>
       </c>
       <c r="G3">
-        <v>1.24243813015582</v>
+        <v>-0.1440267956829178</v>
       </c>
       <c r="H3">
-        <v>1.24243813015582</v>
+        <v>-0.1440267956829178</v>
       </c>
       <c r="I3">
-        <v>0.694775435380385</v>
+        <v>0.7610718273167101</v>
       </c>
       <c r="J3">
-        <v>0.694775435380385</v>
+        <v>0.7284378725645235</v>
       </c>
       <c r="K3">
-        <v>-37</v>
+        <v>183.9</v>
       </c>
       <c r="L3">
-        <v>-0.1695692025664528</v>
+        <v>0.6844064011909193</v>
       </c>
       <c r="M3">
-        <v>44.26</v>
+        <v>49.17599999999999</v>
       </c>
       <c r="N3">
-        <v>0.03531758697733801</v>
+        <v>0.0360210958101377</v>
       </c>
       <c r="O3">
-        <v>-1.196216216216216</v>
+        <v>0.2674061990212072</v>
       </c>
       <c r="P3">
-        <v>42.6</v>
+        <v>48.3</v>
       </c>
       <c r="Q3">
-        <v>0.03399297797638046</v>
+        <v>0.03537943158511573</v>
       </c>
       <c r="R3">
-        <v>-1.151351351351351</v>
+        <v>0.2626427406199021</v>
       </c>
       <c r="S3">
-        <v>1.659999999999997</v>
+        <v>0.8759999999999977</v>
       </c>
       <c r="T3">
-        <v>0.0375056484410302</v>
+        <v>0.01781356759394822</v>
       </c>
       <c r="U3">
-        <v>157.2</v>
+        <v>195</v>
       </c>
       <c r="V3">
-        <v>0.1254388764762209</v>
+        <v>0.1428362144740697</v>
       </c>
       <c r="W3">
-        <v>-0.02321204516938519</v>
+        <v>0.1448601811736904</v>
       </c>
       <c r="X3">
-        <v>0.08653153222725167</v>
+        <v>0.07252687250524646</v>
       </c>
       <c r="Y3">
-        <v>-0.1097435773966369</v>
+        <v>0.07233330866844397</v>
       </c>
       <c r="Z3">
-        <v>0.1411749482401656</v>
+        <v>0.1842430060340099</v>
       </c>
       <c r="AA3">
-        <v>0.09808488612836438</v>
+        <v>0.1342095833503068</v>
       </c>
       <c r="AB3">
-        <v>0.07667290813744146</v>
+        <v>0.0652606114521342</v>
       </c>
       <c r="AC3">
-        <v>0.02141197799092293</v>
+        <v>0.06894897189817263</v>
       </c>
       <c r="AD3">
-        <v>346.1</v>
+        <v>373.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>346.1</v>
+        <v>373.2</v>
       </c>
       <c r="AG3">
-        <v>188.9</v>
+        <v>178.2</v>
       </c>
       <c r="AH3">
-        <v>0.2164071781404364</v>
+        <v>0.2146801656695812</v>
       </c>
       <c r="AI3">
-        <v>0.212762033564886</v>
+        <v>0.1976276212666808</v>
       </c>
       <c r="AJ3">
-        <v>0.1309895291588656</v>
+        <v>0.1154593754049501</v>
       </c>
       <c r="AK3">
-        <v>0.1285471248724056</v>
+        <v>0.1052320774772647</v>
       </c>
       <c r="AL3">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="AM3">
-        <v>10.03</v>
+        <v>6.540000000000001</v>
       </c>
       <c r="AN3">
-        <v>2.263570961412688</v>
+        <v>1.814292659212445</v>
       </c>
       <c r="AO3">
-        <v>14.71844660194175</v>
+        <v>18.09734513274336</v>
       </c>
       <c r="AP3">
-        <v>1.235448005232178</v>
+        <v>0.8663101604278075</v>
       </c>
       <c r="AQ3">
-        <v>15.11465603190429</v>
+        <v>31.26911314984709</v>
       </c>
     </row>
     <row r="4">
@@ -853,46 +856,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.236</v>
+        <v>0.234</v>
       </c>
       <c r="E4">
-        <v>0.185</v>
+        <v>0.103</v>
       </c>
       <c r="G4">
-        <v>0.8798076923076923</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="H4">
-        <v>0.8798076923076923</v>
+        <v>0.580952380952381</v>
       </c>
       <c r="I4">
-        <v>0.8774038461538461</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="J4">
-        <v>0.8557634005453502</v>
+        <v>0.8854368932038835</v>
       </c>
       <c r="K4">
-        <v>26.1</v>
+        <v>30.2</v>
       </c>
       <c r="L4">
-        <v>0.6274038461538461</v>
+        <v>0.4793650793650793</v>
       </c>
       <c r="M4">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="N4">
-        <v>0.03519967064635653</v>
+        <v>0.03705272072835063</v>
       </c>
       <c r="O4">
-        <v>0.6551724137931034</v>
+        <v>0.5794701986754967</v>
       </c>
       <c r="P4">
-        <v>17.1</v>
+        <v>17.5</v>
       </c>
       <c r="Q4">
-        <v>0.03519967064635653</v>
+        <v>0.03705272072835063</v>
       </c>
       <c r="R4">
-        <v>0.6551724137931034</v>
+        <v>0.5794701986754967</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>35.6</v>
+        <v>35.9</v>
       </c>
       <c r="V4">
-        <v>0.07328118567311651</v>
+        <v>0.07601100995130214</v>
       </c>
       <c r="W4">
-        <v>0.04807515196168724</v>
+        <v>0.05811044833557821</v>
       </c>
       <c r="X4">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y4">
-        <v>-0.03026619171942316</v>
+        <v>-0.008678079014833598</v>
       </c>
       <c r="Z4">
-        <v>0.08112324492979721</v>
+        <v>0.1329955668144395</v>
       </c>
       <c r="AA4">
-        <v>0.06942230394439659</v>
+        <v>0.1177591814900668</v>
       </c>
       <c r="AB4">
-        <v>0.0783413436811104</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC4">
-        <v>-0.008919039736713805</v>
+        <v>0.05097065413965503</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -937,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-35.6</v>
+        <v>-35.9</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -946,28 +949,28 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.0790759662372279</v>
+        <v>-0.08226397800183317</v>
       </c>
       <c r="AK4">
-        <v>-0.079269650411935</v>
+        <v>-0.07780667533593411</v>
       </c>
       <c r="AL4">
-        <v>0.184</v>
+        <v>0.139</v>
       </c>
       <c r="AM4">
-        <v>-0.02099999999999999</v>
+        <v>-0.04499999999999998</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
       <c r="AO4">
-        <v>198.3695652173913</v>
+        <v>410.0719424460431</v>
       </c>
       <c r="AP4">
-        <v>-0.9726775956284153</v>
+        <v>-0.6298245614035087</v>
       </c>
       <c r="AQ4">
-        <v>-1738.095238095239</v>
+        <v>-1266.666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Beluga NV (ENXTBR:BELU)</t>
+          <t>Whitestone Group SA (ENXTBR:ROCK)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,112 +990,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.528</v>
+        <v>4.39</v>
       </c>
       <c r="G5">
-        <v>-0.9322916666666666</v>
+        <v>0.009855299178725069</v>
       </c>
       <c r="H5">
-        <v>-0.9322916666666666</v>
+        <v>0.009855299178725069</v>
       </c>
       <c r="I5">
-        <v>-0.8072916666666666</v>
+        <v>0.004536566288619476</v>
       </c>
       <c r="J5">
-        <v>-0.7285315040650406</v>
+        <v>0.002268283144309738</v>
       </c>
       <c r="K5">
-        <v>0.038</v>
+        <v>-0.931</v>
       </c>
       <c r="L5">
-        <v>0.1979166666666667</v>
+        <v>-0.003640985529917873</v>
       </c>
       <c r="M5">
-        <v>0.211</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.05368956743002544</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>5.552631578947368</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>0.211</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.05368956743002544</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>5.552631578947368</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>3.29</v>
+        <v>2.41</v>
       </c>
       <c r="V5">
-        <v>0.8371501272264631</v>
+        <v>0.09450980392156863</v>
       </c>
       <c r="W5">
-        <v>0.006620209059233449</v>
+        <v>-0.0589240506329114</v>
       </c>
       <c r="X5">
-        <v>0.0807334440526585</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="Y5">
-        <v>-0.07411323499342505</v>
+        <v>-0.1257125779833232</v>
       </c>
       <c r="Z5">
-        <v>0.1329639889196675</v>
+        <v>27.00105596620908</v>
       </c>
       <c r="AA5">
-        <v>-0.09686845483413278</v>
+        <v>0.06124604012671594</v>
       </c>
       <c r="AB5">
-        <v>0.07840966213082375</v>
+        <v>0.06678852735041181</v>
       </c>
       <c r="AC5">
-        <v>-0.1752781169649565</v>
+        <v>-0.005542487223695873</v>
       </c>
       <c r="AD5">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.317</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-2.973</v>
+        <v>-2.41</v>
       </c>
       <c r="AH5">
-        <v>0.07464092300447375</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.05285976321494081</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-3.106583072100312</v>
+        <v>-0.1043741879601559</v>
       </c>
       <c r="AK5">
-        <v>-1.098263760620613</v>
+        <v>-0.1760409057706355</v>
       </c>
       <c r="AL5">
-        <v>0.037</v>
+        <v>1.05</v>
       </c>
       <c r="AM5">
-        <v>0.025</v>
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
       </c>
       <c r="AO5">
-        <v>-4.189189189189189</v>
+        <v>1.104761904761905</v>
+      </c>
+      <c r="AP5">
+        <v>-0.9060150375939849</v>
       </c>
       <c r="AQ5">
-        <v>-6.2</v>
+        <v>1.234042553191489</v>
       </c>
     </row>
   </sheetData>
